--- a/artfynd/A 42018-2026 artfynd.xlsx
+++ b/artfynd/A 42018-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137329501</v>
       </c>
       <c r="B2" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42018-2026 artfynd.xlsx
+++ b/artfynd/A 42018-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137329501</v>
       </c>
       <c r="B2" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42018-2026 artfynd.xlsx
+++ b/artfynd/A 42018-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137329501</v>
       </c>
       <c r="B2" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42018-2026 artfynd.xlsx
+++ b/artfynd/A 42018-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137329501</v>
       </c>
       <c r="B2" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42018-2026 artfynd.xlsx
+++ b/artfynd/A 42018-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137329501</v>
       </c>
       <c r="B2" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42018-2026 artfynd.xlsx
+++ b/artfynd/A 42018-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137329501</v>
       </c>
       <c r="B2" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42018-2026 artfynd.xlsx
+++ b/artfynd/A 42018-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137329501</v>
       </c>
       <c r="B2" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
